--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_156_China.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_156_China.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R3ecfc87b60274cf2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R502272d8b3a6406b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R1b6fbd102f1d45fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R4e8814a0571746c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Re12071137f3141c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R7546dd3b827647d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rd141848a84f648ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R1c62281b9dd54964"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R9035dec44b434c36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R9800e4e2749e4611"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R9c82350835b04c4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R2e74437f0545434d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ156CommercialTable" displayName="EEZ156CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ156CommercialTable" displayName="EEZ156CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ156FunctionalTable" displayName="EEZ156FunctionalTable" ref="A1:O23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O23"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ156FunctionalTable" displayName="EEZ156FunctionalTable" ref="A1:E23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E23"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ156ValidationTable" displayName="EEZ156ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ156ValidationTable" displayName="EEZ156ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -12754,7 +12708,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a32785c9cca4885"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96610c0922424c08"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12764,20 +12718,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -12785,660 +12729,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>700510.9995925244</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.14</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>138.03842646028852</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>700510.9995925244</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>138.03842646028852</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$181,A2,'Species'!$U$2:$U$181))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>96697436.10187587</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.14</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>138.03842646028852</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>96697436.10187587</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>14412.5391618758</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.16</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1445.439770745928</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>14412.5391618758</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1445.439770745928</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$181,A3,'Species'!$U$2:$U$181))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>20832457.302008465</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.16</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1445.439770745928</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>20832457.302008465</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1787743.256493882</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.8975556871432246</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>78.98701235183387</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1787743.256493882</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>167.94829922745112</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$181,A4,'Species'!$U$2:$U$181))</x:f>
-        <x:v>300248439.3834924</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.8975556871432246</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>78.98701235183387</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>141208498.68258998</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>159039940.70090243</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>2.1262773996230506</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>1.1262773996230508</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>30904.1105627735</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.3663189598857493</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>232.4443315818871</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>30904.1105627735</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>450.56851195157714</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$181,A5,'Species'!$U$2:$U$181))</x:f>
-        <x:v>13924419.109455874</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.3663189598857493</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>232.4443315818871</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>7183485.322896623</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>6740933.786559251</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.9383932010097127</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.9383932010097126</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>150299.49554733242</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.1879615889443507</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>154.15641037080596</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>150299.49554733242</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>248.96971020067437</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$181,A6,'Species'!$U$2:$U$181))</x:f>
-        <x:v>37420021.8497269</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.1879615889443507</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>154.15641037080596</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>23169630.7141197</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>14250391.135607202</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.6150461054574743</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.6150461054574744</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>51889.752628545706</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.325219611598117</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>21.14558047384111</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>51889.752628545706</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>39.56336004404221</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$181,A7,'Species'!$U$2:$U$181))</x:f>
-        <x:v>2052932.9658394395</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.325219611598117</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>21.14558047384111</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1097238.9399746216</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>955694.0258648179</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.870999005819938</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.8709990058199378</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>3500048.5447079586</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6076133634036305</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>405.1476865833035</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>3500048.5447079586</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>626.0528545119382</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$181,A8,'Species'!$U$2:$U$181))</x:f>
-        <x:v>2191215382.344773</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6076133634036305</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>405.1476865833035</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1418036570.8176875</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>773178811.5270853</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.545246030630398</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.5452460306303979</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>3288991.4931474067</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.754724876427865</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>568.4926792293614</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>3288991.4931474067</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1048.8743222407672</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$181,A9,'Species'!$U$2:$U$181))</x:f>
-        <x:v>3449738723.230635</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.754724876427865</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>568.4926792293614</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1869767585.9019473</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1579971137.328688</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.845009374021496</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.8450093740214959</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>6541.1110847639</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.6990077443420564</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>500.04345167559455</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>6541.1110847639</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>508.7423111431647</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$181,A10,'Species'!$U$2:$U$181))</x:f>
-        <x:v>3327739.9707069597</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.6990077443420564</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>500.04345167559455</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>3270839.764618833</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>56900.20608812664</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0173962071464413</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.017396207146441335</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>29378.0798257328</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.0672932190245294</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1167.5976682906992</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>29378.0798257328</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1200.359165660854</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$181,A11,'Species'!$U$2:$U$181))</x:f>
-        <x:v>35264247.38833459</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.0672932190245294</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1167.5976682906992</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>34301777.503383644</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>962469.8849509433</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0280588924249188</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.028058892424918856</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>7421.214977494699</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.300614530549541</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1998.0876273172207</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>7421.214977494699</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2035.62453686499</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$181,A12,'Species'!$U$2:$U$181))</x:f>
-        <x:v>15106807.301538175</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.300614530549541</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1998.0876273172207</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>14828237.826193405</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>278569.47534476966</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0187864180902662</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.01878641809026622</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ba6c89936ab4094"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31530b49ae85422a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13448,20 +12963,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -13469,1254 +12974,440 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>609989.8958345469</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.012470831110888</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1029.1314044466744</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>609989.8958345469</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1200.2556406779374</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$181,A2,'Species'!$U$2:$U$181))</x:f>
-        <x:v>732143813.2319623</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.012470831110888</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1029.1314044466744</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>627759758.1984879</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>104384055.03347445</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.166280258761776</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.1662802587617759</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1437809.0859416688</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.4337826182097415</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>271.5079922370089</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1437809.0859416688</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>284.2062906869925</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$181,A3,'Species'!$U$2:$U$181))</x:f>
-        <x:v>408634387.0315369</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.4337826182097415</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>271.5079922370089</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>390376658.1441515</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>18257728.88738537</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.046769519914901</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.046769519914900935</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>771642.2209903115</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.230914074893793</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1701.8217698705496</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>771642.2209903115</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2368.74510001742</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$181,A4,'Species'!$U$2:$U$181))</x:f>
-        <x:v>1827823729.9373596</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.230914074893793</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1701.8217698705496</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1313197530.2325735</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>514626199.70478606</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.3918878827114785</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.39188788271147856</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>235483.68150219918</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.343599052220558</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2205.9672075653884</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>235483.68150219918</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2270.015003002199</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$181,A5,'Species'!$U$2:$U$181))</x:f>
-        <x:v>534551489.9721836</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.343599052220558</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2205.9672075653884</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>519469279.31062365</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>15082210.66155994</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0290338837391408</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.029033883739140863</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>5700.4175110233</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.25</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1778.2794100389228</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>5700.4175110233</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1778.2794100389228</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$181,A6,'Species'!$U$2:$U$181))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>10136935.088478059</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.25</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1778.2794100389228</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>10136935.088478059</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>331565.76807735587</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.383007460754671</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2415.50233005736</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>331565.76807735587</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2442.4873238331165</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$181,A7,'Species'!$U$2:$U$181))</x:f>
-        <x:v>809845185.5459327</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.383007460754671</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2415.50233005736</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>800897885.3581113</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>8947300.187821388</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0111715867295876</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.011171586729587527</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>0.1251043766</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.84</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>691.8309709189363</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>0.1251043766</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>691.8309709189363</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$181,A8,'Species'!$U$2:$U$181))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>86.55108232938626</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.84</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>691.8309709189363</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>86.55108232938626</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>10356.063652305</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.733378809091659</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>541.2261963503795</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>10356.063652305</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>639.2669559740539</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$181,A9,'Species'!$U$2:$U$181))</x:f>
-        <x:v>6620289.28688256</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.733378809091659</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>541.2261963503795</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>5604972.939699454</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1015316.3471831055</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1811456287311797</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.1811456287311796</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>29377.9547213562</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.067294186939987</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1167.6002705275162</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>29377.9547213562</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1200.361331199721</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$181,A10,'Species'!$U$2:$U$181))</x:f>
-        <x:v>35264160.83725226</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.067294186939987</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1167.6002705275162</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>34301707.88020062</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>962452.9570516422</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0280584558766879</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.02805845587668777</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>635863.1236255732</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.3141963504966556</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>206.1561762974383</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>635863.1236255732</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>334.33054808847874</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$181,A11,'Species'!$U$2:$U$181))</x:f>
-        <x:v>212588466.63099003</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.3141963504966556</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>206.1561762974383</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>131087110.21519348</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>81501356.41579655</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.6217343282799002</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.6217343282799</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>740196.5227352128</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.609808236727779</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>407.2004382395225</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>740196.5227352128</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>532.7423575621807</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$181,A12,'Species'!$U$2:$U$181))</x:f>
-        <x:v>394334040.5812856</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.609808236727779</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>407.2004382395225</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>301408348.44114935</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>92925692.14013624</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.3083049710492016</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.3083049710492017</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>898577.2660387392</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.350145899201123</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>223.94733528144857</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>898577.2660387392</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>290.8670024553806</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$181,A13,'Species'!$U$2:$U$181))</x:f>
-        <x:v>261366475.84723914</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.350145899201123</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>223.94733528144857</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>201233984.27386495</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>60132491.57337418</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.298818769555038</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.29881876955503794</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>1058842.8346662621</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.5281237428429466</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>337.38342509317937</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>1058842.8346662621</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>414.98641729436724</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$181,A14,'Species'!$U$2:$U$181))</x:f>
-        <x:v>439405394.43596417</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.5281237428429466</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>337.38342509317937</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>357236022.19507456</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>82169372.24088961</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.2300142402661165</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.2300142402661165</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>499720.28623948456</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.3685539012677936</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>233.64360645749275</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>499720.28623948456</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>296.94668804911305</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$181,A15,'Species'!$U$2:$U$181))</x:f>
-        <x:v>148390283.9497697</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.3685539012677936</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>233.64360645749275</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>116756449.89696376</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>31633834.052805945</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.270938642625075</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.27093864262507505</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>92667.89466727071</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.3711017879834824</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>23.50183581739938</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>92667.89466727071</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>34.03213083106816</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$181,A16,'Species'!$U$2:$U$181))</x:f>
-        <x:v>3153685.9151562</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.3711017879834824</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>23.50183581739938</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>2177865.646014256</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>975820.2691419441</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.448062657550895</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.4480626575508949</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>1151880.132868309</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.6675608933536585</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>46.511558644118914</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>1151880.132868309</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>76.10164482498654</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$181,A17,'Species'!$U$2:$U$181))</x:f>
-        <x:v>87659972.75250235</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.6675608933536585</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>46.511558644118914</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>53575740.350899845</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>34084232.40160251</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.6361878002686348</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.6361878002686348</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small bathydemersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>7383.935699065601</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.51</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>323.5936569296281</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>7383.935699065601</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>323.5936569296281</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$181,A18,'Species'!$U$2:$U$181))</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>2389394.7553938674</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.51</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>323.5936569296281</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
-        <x:v>2389394.7553938674</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>14584.0283912924</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.8480589764447686</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>704.7887715736236</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>14584.0283912924</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>766.7927364090737</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$181,A19,'Species'!$U$2:$U$181))</x:f>
-        <x:v>11182927.03802672</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.8480589764447686</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>704.7887715736236</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>10278659.454493823</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>904267.5835328978</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0879752449758955</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.08797524497589543</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>278864.2822514818</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.6770267243186177</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>475.3644766042934</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>278864.2822514818</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>485.7433103670532</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$181,A20,'Species'!$U$2:$U$181))</x:f>
-        <x:v>135456459.60396704</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.6770267243186177</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>475.3644766042934</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>132562173.57610758</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>2894286.0278594643</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0218334231385982</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.02183342313859825</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>730806.6311900263</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.138649479625694</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>137.6098367462539</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>730806.6311900263</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>138.0455935950613</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$181,A21,'Species'!$U$2:$U$181))</x:f>
-        <x:v>100884635.20583421</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.138649479625694</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>137.6098367462539</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>100566181.2111393</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>318453.9946949035</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0031666111893651</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.003166611189365015</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>1624.7529706802</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>1624.7529706802</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$181,A22,'Species'!$U$2:$U$181))</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>209308.7286090855</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
-        <x:v>209308.7286090855</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>25203.6930517502</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.166453374120859</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>146.70785728173644</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>25203.6930517502</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>150.27496221292077</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$181,A23,'Species'!$U$2:$U$181))</x:f>
-        <x:v>3787484.020977815</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.166453374120859</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>146.70785728173644</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>3697579.8032088606</x:v>
       </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>89904.21776895458</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.024314341421633</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.02431434142163294</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G23">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O23">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca3d2aebe180418a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc752bc4c182a402a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14891,7 +13582,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -14990,7 +13681,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>6165828606.948386</x:v>
+        <x:v>3630393758.877296</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15004,7 +13695,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>6165828606.948386</x:v>
+        <x:v>5114923632.251522</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15018,7 +13709,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-2535434848.07109</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15032,7 +13723,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-1050904974.6968641</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15043,9 +13734,9 @@
         <x:v>EEZ_156</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -15057,47 +13748,19 @@
         <x:v>EEZ_156</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_156</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_156</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8af53f5bc11d4ada"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb558e7a042254ab4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15144,7 +13807,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
